--- a/output/daily_screen_20261016.xlsx
+++ b/output/daily_screen_20261016.xlsx
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -703,7 +703,7 @@
         <v>19.54999923706055</v>
       </c>
       <c r="R2" t="n">
-        <v>65846976</v>
+        <v>65670302</v>
       </c>
       <c r="S2" t="n">
         <v>19.32999992370605</v>
@@ -718,16 +718,16 @@
         <v>19.03753280639648</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1408405378258699</v>
+        <v>0.1408405378258664</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06601432902447982</v>
+        <v>0.06601432902447313</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0748262088013901</v>
+        <v>0.07482620880139323</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.06175010322038849</v>
+        <v>0.06175010322038885</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>61.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -845,7 +845,7 @@
         <v>176</v>
       </c>
       <c r="R3" t="n">
-        <v>1711116</v>
+        <v>1689482</v>
       </c>
       <c r="S3" t="n">
         <v>174.8</v>
@@ -860,16 +860,16 @@
         <v>184.3876274108887</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.427535160659488</v>
+        <v>-1.427535160659517</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.096546092956168</v>
+        <v>-3.096546092956211</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.66901093229668</v>
+        <v>1.669010932296694</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.660792931061975</v>
+        <v>1.660792931061994</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>76.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6700000</v>
+        <v>6899000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
@@ -972,13 +972,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5808000</v>
+        <v>6700000</v>
       </c>
       <c r="N4" t="n">
-        <v>892000</v>
+        <v>199000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1535812672176309</v>
+        <v>0.02970149253731343</v>
       </c>
       <c r="P4" t="n">
         <v>1245</v>
@@ -987,7 +987,7 @@
         <v>1245</v>
       </c>
       <c r="R4" t="n">
-        <v>15727206</v>
+        <v>15215404</v>
       </c>
       <c r="S4" t="n">
         <v>1220</v>
@@ -1005,13 +1005,13 @@
         <v>38.14472539795747</v>
       </c>
       <c r="X4" t="n">
-        <v>38.55835926692416</v>
+        <v>38.55835926692415</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.4136338689666914</v>
+        <v>-0.4136338689666772</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.5591652991634533</v>
+        <v>-0.559165299163439</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1127,7 +1127,7 @@
         <v>557</v>
       </c>
       <c r="R5" t="n">
-        <v>28104300</v>
+        <v>27282900</v>
       </c>
       <c r="S5" t="n">
         <v>555.2</v>
@@ -1145,13 +1145,13 @@
         <v>13.0298655157427</v>
       </c>
       <c r="X5" t="n">
-        <v>17.33104492404922</v>
+        <v>17.33104492404919</v>
       </c>
       <c r="Y5" t="n">
-        <v>-4.301179408306524</v>
+        <v>-4.301179408306488</v>
       </c>
       <c r="Z5" t="n">
-        <v>-4.317652886009135</v>
+        <v>-4.317652886009089</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.40000000000001</v>
+        <v>47.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>248</v>
       </c>
       <c r="R6" t="n">
-        <v>50253773</v>
+        <v>49130197</v>
       </c>
       <c r="S6" t="n">
         <v>244.4</v>
@@ -1285,13 +1285,13 @@
         <v>3.972947556634949</v>
       </c>
       <c r="X6" t="n">
-        <v>4.107292513375468</v>
+        <v>4.107292513375461</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1343449567405184</v>
+        <v>-0.1343449567405113</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.5706998436825916</v>
+        <v>-0.5706998436825819</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.2</v>
+        <v>59.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1375,15 +1375,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7224000</v>
+        <v>19499000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1392,73 +1392,73 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7046000</v>
+        <v>19386000</v>
       </c>
       <c r="N7" t="n">
-        <v>178000</v>
+        <v>113000</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02526256031791087</v>
+        <v>0.005828948725884659</v>
       </c>
       <c r="P7" t="n">
-        <v>1615</v>
+        <v>1090</v>
       </c>
       <c r="Q7" t="n">
-        <v>1615</v>
+        <v>1090</v>
       </c>
       <c r="R7" t="n">
-        <v>10975718</v>
+        <v>14516214</v>
       </c>
       <c r="S7" t="n">
-        <v>1673</v>
+        <v>1157</v>
       </c>
       <c r="T7" t="n">
-        <v>1572.75</v>
+        <v>1161.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1560.5</v>
+        <v>1154.15</v>
       </c>
       <c r="V7" t="n">
-        <v>1459.75</v>
+        <v>1035.883333333333</v>
       </c>
       <c r="W7" t="n">
-        <v>45.02341109165354</v>
+        <v>4.353879746731536</v>
       </c>
       <c r="X7" t="n">
-        <v>59.69238685971857</v>
+        <v>38.65338220905522</v>
       </c>
       <c r="Y7" t="n">
-        <v>-14.66897576806503</v>
+        <v>-34.29950246232368</v>
       </c>
       <c r="Z7" t="n">
-        <v>-5.628074490698374</v>
+        <v>-29.62678598084111</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1788321167883211</v>
+        <v>0.1461619348054679</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3212121212121213</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1436811362795365</v>
+        <v>0.1110109542966833</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2426187424041908</v>
+        <v>0.2561385559240044</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0989376061246543</v>
+        <v>-0.1451276016273211</v>
       </c>
       <c r="AG7" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
@@ -1473,11 +1473,9 @@
         <v>0</v>
       </c>
       <c r="AN7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1782.96</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -1492,12 +1490,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1506,7 +1504,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60.8</v>
+        <v>53.40000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1515,87 +1513,87 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19386000</v>
+        <v>852000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>18938000</v>
+        <v>751000</v>
       </c>
       <c r="N8" t="n">
-        <v>448000</v>
+        <v>101000</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02365614109198437</v>
+        <v>0.1344873501997337</v>
       </c>
       <c r="P8" t="n">
-        <v>1090</v>
+        <v>7480</v>
       </c>
       <c r="Q8" t="n">
-        <v>1090</v>
+        <v>7480</v>
       </c>
       <c r="R8" t="n">
-        <v>14914936</v>
+        <v>1804746</v>
       </c>
       <c r="S8" t="n">
-        <v>1157</v>
+        <v>7918</v>
       </c>
       <c r="T8" t="n">
-        <v>1161.1</v>
+        <v>7893.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1154.15</v>
+        <v>7821.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1035.883333333333</v>
+        <v>6090.5</v>
       </c>
       <c r="W8" t="n">
-        <v>4.353879746731536</v>
+        <v>140.3120352777469</v>
       </c>
       <c r="X8" t="n">
-        <v>38.65338220905522</v>
+        <v>342.9687652512529</v>
       </c>
       <c r="Y8" t="n">
-        <v>-34.29950246232368</v>
+        <v>-202.6567299735061</v>
       </c>
       <c r="Z8" t="n">
-        <v>-29.62678598084111</v>
+        <v>-162.3819064662263</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1461619348054679</v>
+        <v>0.2394366197183098</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3212121212121213</v>
+        <v>0.8177399756986634</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.1110109542966833</v>
+        <v>0.2042856392095251</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.2561385559240044</v>
+        <v>0.7526664104105465</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.1451276016273211</v>
+        <v>-0.5483807712010214</v>
       </c>
       <c r="AG8" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH8" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -1630,12 +1628,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1644,7 +1642,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57.2</v>
+        <v>52.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1653,15 +1651,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>981000</v>
+        <v>2657000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1670,70 +1668,70 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>696000</v>
+        <v>1857000</v>
       </c>
       <c r="N9" t="n">
-        <v>285000</v>
+        <v>800000</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4094827586206897</v>
+        <v>0.4308023694130318</v>
       </c>
       <c r="P9" t="n">
-        <v>1570</v>
+        <v>258.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1570</v>
+        <v>258.5</v>
       </c>
       <c r="R9" t="n">
-        <v>6008077</v>
+        <v>23753240</v>
       </c>
       <c r="S9" t="n">
-        <v>1642</v>
+        <v>269.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1564.25</v>
+        <v>255.45</v>
       </c>
       <c r="U9" t="n">
-        <v>1546.75</v>
+        <v>253.575</v>
       </c>
       <c r="V9" t="n">
-        <v>1279.55</v>
+        <v>227.675</v>
       </c>
       <c r="W9" t="n">
-        <v>44.2140083672773</v>
+        <v>6.416139638692187</v>
       </c>
       <c r="X9" t="n">
-        <v>69.49502928741238</v>
+        <v>6.022033229720711</v>
       </c>
       <c r="Y9" t="n">
-        <v>-25.28102092013508</v>
+        <v>0.3941064089714752</v>
       </c>
       <c r="Z9" t="n">
-        <v>-19.03649200108956</v>
+        <v>1.892489559765102</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.2868852459016393</v>
+        <v>0.1696832579185521</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.5971515768056967</v>
+        <v>0.230952380952381</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2517342653928547</v>
+        <v>0.1345322774097675</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.5320780115175798</v>
+        <v>0.1658788156642641</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2803437461247251</v>
+        <v>-0.03134653825449663</v>
       </c>
       <c r="AG9" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="AH9" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
@@ -1742,10 +1740,10 @@
         <v>1</v>
       </c>
       <c r="AK9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" t="b">
         <v>0</v>
@@ -1753,8 +1751,10 @@
       <c r="AN9" t="b">
         <v>0</v>
       </c>
-      <c r="AO9" t="n">
-        <v>1855.74</v>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1784,24 +1784,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>54.6</v>
+        <v>52.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6303000</v>
+        <v>7224000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1810,73 +1810,73 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6147000</v>
+        <v>7224000</v>
       </c>
       <c r="N10" t="n">
-        <v>156000</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02537823328452904</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3315</v>
+        <v>1615</v>
       </c>
       <c r="Q10" t="n">
-        <v>3315</v>
+        <v>1615</v>
       </c>
       <c r="R10" t="n">
-        <v>3730261</v>
+        <v>10612264</v>
       </c>
       <c r="S10" t="n">
-        <v>3276</v>
+        <v>1673</v>
       </c>
       <c r="T10" t="n">
-        <v>3402</v>
+        <v>1572.75</v>
       </c>
       <c r="U10" t="n">
-        <v>3392</v>
+        <v>1560.5</v>
       </c>
       <c r="V10" t="n">
-        <v>3093.299527994792</v>
+        <v>1459.75</v>
       </c>
       <c r="W10" t="n">
-        <v>-35.3894972052758</v>
+        <v>45.02341109165354</v>
       </c>
       <c r="X10" t="n">
-        <v>13.16323473578665</v>
+        <v>59.69238685971835</v>
       </c>
       <c r="Y10" t="n">
-        <v>-48.55273194106245</v>
+        <v>-14.6689757680648</v>
       </c>
       <c r="Z10" t="n">
-        <v>-62.50287942092719</v>
+        <v>-5.62807449069809</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0642054574638844</v>
+        <v>0.1788321167883211</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.437355921588952</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.02905447695509977</v>
+        <v>0.1436811362795365</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.3722823563008351</v>
+        <v>0.2426187424041908</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.3432278793457353</v>
+        <v>-0.0989376061246543</v>
       </c>
       <c r="AG10" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="AH10" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="b">
         <v>1</v>
@@ -1888,13 +1888,13 @@
         <v>0</v>
       </c>
       <c r="AM10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="b">
         <v>1</v>
       </c>
       <c r="AO10" t="n">
-        <v>3865.29</v>
+        <v>1782.96</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1924,96 +1924,96 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>52.2</v>
+        <v>51.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1857000</v>
+        <v>8937000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1257000</v>
+        <v>8937000</v>
       </c>
       <c r="N11" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.477326968973747</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>258.5</v>
+        <v>1355</v>
       </c>
       <c r="Q11" t="n">
-        <v>258.5</v>
+        <v>1355</v>
       </c>
       <c r="R11" t="n">
-        <v>24088759</v>
+        <v>8990416</v>
       </c>
       <c r="S11" t="n">
-        <v>269.1</v>
+        <v>1402</v>
       </c>
       <c r="T11" t="n">
-        <v>255.45</v>
+        <v>1320</v>
       </c>
       <c r="U11" t="n">
-        <v>253.575</v>
+        <v>1306.5</v>
       </c>
       <c r="V11" t="n">
-        <v>227.675</v>
+        <v>1189.416666666667</v>
       </c>
       <c r="W11" t="n">
-        <v>6.416139638692187</v>
+        <v>41.30080840777782</v>
       </c>
       <c r="X11" t="n">
-        <v>6.022033229720711</v>
+        <v>63.62982051017949</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3941064089714752</v>
+        <v>-22.32901210240167</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.892489559765102</v>
+        <v>-15.92441011774856</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1696832579185521</v>
+        <v>0.2488479262672811</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.230952380952381</v>
+        <v>0.1386554621848739</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1345322774097675</v>
+        <v>0.2136969457584965</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1658788156642641</v>
+        <v>0.07358189689675698</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.03134653825449663</v>
+        <v>0.1401150488617395</v>
       </c>
       <c r="AG11" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AH11" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2022,10 +2022,10 @@
         <v>1</v>
       </c>
       <c r="AK11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="b">
         <v>0</v>
@@ -2033,10 +2033,8 @@
       <c r="AN11" t="b">
         <v>0</v>
       </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO11" t="n">
+        <v>1607.03</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2052,12 +2050,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2066,99 +2064,99 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>51.2</v>
+        <v>48.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8937000</v>
+        <v>769000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>8937000</v>
+        <v>649000</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.1848998459167951</v>
       </c>
       <c r="P12" t="n">
-        <v>1355</v>
+        <v>2250</v>
       </c>
       <c r="Q12" t="n">
-        <v>1355</v>
+        <v>2250</v>
       </c>
       <c r="R12" t="n">
-        <v>9127777</v>
+        <v>1747205</v>
       </c>
       <c r="S12" t="n">
-        <v>1402</v>
+        <v>2208</v>
       </c>
       <c r="T12" t="n">
-        <v>1320</v>
+        <v>2343.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1306.5</v>
+        <v>2332.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1189.416666666667</v>
+        <v>2005.600705973307</v>
       </c>
       <c r="W12" t="n">
-        <v>41.30080840777782</v>
+        <v>-27.82926529920223</v>
       </c>
       <c r="X12" t="n">
-        <v>63.62982051017935</v>
+        <v>16.09219857541557</v>
       </c>
       <c r="Y12" t="n">
-        <v>-22.32901210240153</v>
+        <v>-43.9214638746178</v>
       </c>
       <c r="Z12" t="n">
-        <v>-15.92441011774838</v>
+        <v>-56.51359028373258</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2488479262672811</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1386554621848739</v>
+        <v>0.6012255213039355</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.2136969457584965</v>
+        <v>0.07596013060232654</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.07358189689675698</v>
+        <v>0.5361519560158186</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1401150488617395</v>
+        <v>-0.460191825413492</v>
       </c>
       <c r="AG12" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="AI12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
@@ -2170,14 +2168,12 @@
         <v>0</v>
       </c>
       <c r="AM12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="b">
         <v>0</v>
       </c>
-      <c r="AO12" t="n">
-        <v>1607.03</v>
-      </c>
+      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2192,12 +2188,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2206,24 +2202,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>649000</v>
+        <v>1000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2232,90 +2228,94 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>499000</v>
+        <v>1000</v>
       </c>
       <c r="N13" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3006012024048096</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2250</v>
+        <v>298.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2250</v>
+        <v>298.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1783307</v>
+        <v>39659568</v>
       </c>
       <c r="S13" t="n">
-        <v>2208</v>
+        <v>285.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2343.75</v>
+        <v>232</v>
       </c>
       <c r="U13" t="n">
-        <v>2332.5</v>
+        <v>226.1</v>
       </c>
       <c r="V13" t="n">
-        <v>2005.600705973307</v>
+        <v>194.0583333333333</v>
       </c>
       <c r="W13" t="n">
-        <v>-27.82926529920223</v>
+        <v>24.41714981393159</v>
       </c>
       <c r="X13" t="n">
-        <v>16.09219857541557</v>
+        <v>17.18132826767883</v>
       </c>
       <c r="Y13" t="n">
-        <v>-43.9214638746178</v>
+        <v>7.235821546252758</v>
       </c>
       <c r="Z13" t="n">
-        <v>-56.51359028373258</v>
+        <v>7.992130067756985</v>
       </c>
       <c r="AA13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1111111111111112</v>
+        <v>0.6537396121883656</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.6012255213039355</v>
+        <v>0.7874251497005988</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.07596013060232654</v>
+        <v>0.618588631679581</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5361519560158186</v>
+        <v>0.7223515844124819</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.460191825413492</v>
+        <v>-0.1037629527329009</v>
       </c>
       <c r="AG13" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AH13" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AI13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="b">
         <v>0</v>
       </c>
-      <c r="AO13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
       <c r="AP13" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>47.8</v>
+        <v>46.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2353,15 +2353,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1000</v>
+        <v>981000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1000</v>
+        <v>981000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2379,61 +2379,61 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>298.5</v>
+        <v>1570</v>
       </c>
       <c r="Q14" t="n">
-        <v>298.5</v>
+        <v>1570</v>
       </c>
       <c r="R14" t="n">
-        <v>39973694</v>
+        <v>5916466</v>
       </c>
       <c r="S14" t="n">
-        <v>285.6</v>
+        <v>1642</v>
       </c>
       <c r="T14" t="n">
-        <v>232</v>
+        <v>1564.25</v>
       </c>
       <c r="U14" t="n">
-        <v>226.1</v>
+        <v>1546.75</v>
       </c>
       <c r="V14" t="n">
-        <v>194.0583333333333</v>
+        <v>1279.55</v>
       </c>
       <c r="W14" t="n">
-        <v>24.41714981393159</v>
+        <v>44.2140083672773</v>
       </c>
       <c r="X14" t="n">
-        <v>17.18132826767882</v>
+        <v>69.49502928741234</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.235821546252765</v>
+        <v>-25.28102092013503</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.992130067756996</v>
+        <v>-19.03649200108951</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.6537396121883656</v>
+        <v>0.2868852459016393</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.7874251497005988</v>
+        <v>0.5971515768056967</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.618588631679581</v>
+        <v>0.2517342653928547</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.7223515844124819</v>
+        <v>0.5320780115175798</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.1037629527329009</v>
+        <v>-0.2803437461247251</v>
       </c>
       <c r="AG14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AH14" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2442,10 +2442,10 @@
         <v>1</v>
       </c>
       <c r="AK14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="b">
         <v>0</v>
@@ -2453,10 +2453,8 @@
       <c r="AN14" t="b">
         <v>0</v>
       </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+      <c r="AO14" t="n">
+        <v>1855.74</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2486,7 +2484,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>46.40000000000001</v>
+        <v>46.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2493,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2503,7 +2501,7 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2527,7 +2525,7 @@
         <v>6730</v>
       </c>
       <c r="R15" t="n">
-        <v>1131578</v>
+        <v>1099414</v>
       </c>
       <c r="S15" t="n">
         <v>6943</v>
@@ -2545,13 +2543,13 @@
         <v>189.7397046221449</v>
       </c>
       <c r="X15" t="n">
-        <v>281.7342017135096</v>
+        <v>281.7342017135097</v>
       </c>
       <c r="Y15" t="n">
-        <v>-91.99449709136468</v>
+        <v>-91.99449709136474</v>
       </c>
       <c r="Z15" t="n">
-        <v>-66.55202090973768</v>
+        <v>-66.55202090973779</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -2612,12 +2610,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2626,7 +2624,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>44.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2635,24 +2633,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>751000</v>
+        <v>6303000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>751000</v>
+        <v>6303000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2661,61 +2659,61 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>7480</v>
+        <v>3315</v>
       </c>
       <c r="Q16" t="n">
-        <v>7480</v>
+        <v>3315</v>
       </c>
       <c r="R16" t="n">
-        <v>1890956</v>
+        <v>3569214</v>
       </c>
       <c r="S16" t="n">
-        <v>7918</v>
+        <v>3276</v>
       </c>
       <c r="T16" t="n">
-        <v>7893.5</v>
+        <v>3402</v>
       </c>
       <c r="U16" t="n">
-        <v>7821.25</v>
+        <v>3392</v>
       </c>
       <c r="V16" t="n">
-        <v>6090.5</v>
+        <v>3093.299527994792</v>
       </c>
       <c r="W16" t="n">
-        <v>140.3120352777469</v>
+        <v>-35.3894972052758</v>
       </c>
       <c r="X16" t="n">
-        <v>342.9687652512529</v>
+        <v>13.16323473578665</v>
       </c>
       <c r="Y16" t="n">
-        <v>-202.6567299735061</v>
+        <v>-48.55273194106245</v>
       </c>
       <c r="Z16" t="n">
-        <v>-162.3819064662263</v>
+        <v>-62.50287942092719</v>
       </c>
       <c r="AA16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2394366197183098</v>
+        <v>0.0642054574638844</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.8177399756986634</v>
+        <v>0.437355921588952</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.2042856392095251</v>
+        <v>0.02905447695509977</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.7526664104105465</v>
+        <v>0.3722823563008351</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.5483807712010214</v>
+        <v>-0.3432278793457353</v>
       </c>
       <c r="AG16" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="AH16" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
@@ -2730,12 +2728,14 @@
         <v>0</v>
       </c>
       <c r="AM16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>3865.29</v>
+      </c>
       <c r="AP16" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2805,7 +2805,7 @@
         <v>671</v>
       </c>
       <c r="R17" t="n">
-        <v>19182798</v>
+        <v>18315373</v>
       </c>
       <c r="S17" t="n">
         <v>718.6</v>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2902,99 +2902,99 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>40.6</v>
+        <v>43.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>121000</v>
+        <v>12392000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>121000</v>
+        <v>12188000</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>204000</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.01673777486051854</v>
       </c>
       <c r="P18" t="n">
-        <v>1410</v>
+        <v>2420</v>
       </c>
       <c r="Q18" t="n">
-        <v>1410</v>
+        <v>2420</v>
       </c>
       <c r="R18" t="n">
-        <v>2929194</v>
+        <v>33490270</v>
       </c>
       <c r="S18" t="n">
-        <v>1523</v>
+        <v>2476</v>
       </c>
       <c r="T18" t="n">
-        <v>1374</v>
+        <v>2491</v>
       </c>
       <c r="U18" t="n">
-        <v>1364.25</v>
+        <v>2488.9</v>
       </c>
       <c r="V18" t="n">
-        <v>1251.276076253255</v>
+        <v>2416.497591145833</v>
       </c>
       <c r="W18" t="n">
-        <v>44.93885460905562</v>
+        <v>-3.262306824247389</v>
       </c>
       <c r="X18" t="n">
-        <v>57.32524539374288</v>
+        <v>17.31173417264522</v>
       </c>
       <c r="Y18" t="n">
-        <v>-12.38639078468725</v>
+        <v>-20.57404099689261</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.216688377404445</v>
+        <v>-15.91550092530764</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.1604938271604939</v>
+        <v>0.01766190075693852</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.430784538209011</v>
+        <v>0.007105186261707974</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1253428466517092</v>
+        <v>-0.0174890797518461</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.3657109729208941</v>
+        <v>-0.05796837902640894</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.2403681262691848</v>
+        <v>0.04047929927456284</v>
       </c>
       <c r="AG18" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AH18" t="n">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="AI18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
@@ -3012,7 +3012,7 @@
         <v>1</v>
       </c>
       <c r="AO18" t="n">
-        <v>1551</v>
+        <v>2652.32</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3042,24 +3042,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>39.4</v>
+        <v>42.59999999999999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1000</v>
+        <v>5151450</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3068,70 +3068,70 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1000</v>
+        <v>4143450</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1008000</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.2432755312601817</v>
       </c>
       <c r="P19" t="n">
-        <v>105.5</v>
+        <v>275</v>
       </c>
       <c r="Q19" t="n">
-        <v>105.5</v>
+        <v>275</v>
       </c>
       <c r="R19" t="n">
-        <v>19183974</v>
+        <v>16768982</v>
       </c>
       <c r="S19" t="n">
-        <v>113.4</v>
+        <v>289.7</v>
       </c>
       <c r="T19" t="n">
-        <v>111.5899997711182</v>
+        <v>293.825</v>
       </c>
       <c r="U19" t="n">
-        <v>110.5349998474121</v>
+        <v>292.925</v>
       </c>
       <c r="V19" t="n">
-        <v>95.91499989827474</v>
+        <v>265.2283131917318</v>
       </c>
       <c r="W19" t="n">
-        <v>1.714176809923529</v>
+        <v>-0.5994197869163145</v>
       </c>
       <c r="X19" t="n">
-        <v>5.27033707690464</v>
+        <v>4.535897191209457</v>
       </c>
       <c r="Y19" t="n">
-        <v>-3.55616026698111</v>
+        <v>-5.135316978125772</v>
       </c>
       <c r="Z19" t="n">
-        <v>-2.843717107570892</v>
+        <v>-4.22195394856811</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.249999977401083</v>
+        <v>0.07003891050583655</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.01442307692307687</v>
+        <v>0.03889851301655267</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.2148489968922984</v>
+        <v>0.03488792999705193</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.05065048836504005</v>
+        <v>-0.02617505227156425</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.2654994852573385</v>
+        <v>0.06106298226861617</v>
       </c>
       <c r="AG19" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="AH19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3180,102 +3180,102 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36.4</v>
+        <v>40.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7507000</v>
+        <v>121000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7389000</v>
+        <v>121000</v>
       </c>
       <c r="N20" t="n">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.015969684666396</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1635</v>
+        <v>1410</v>
       </c>
       <c r="Q20" t="n">
-        <v>1635</v>
+        <v>1410</v>
       </c>
       <c r="R20" t="n">
-        <v>8576514</v>
+        <v>2852725</v>
       </c>
       <c r="S20" t="n">
-        <v>1745</v>
+        <v>1523</v>
       </c>
       <c r="T20" t="n">
-        <v>1848.25</v>
+        <v>1374</v>
       </c>
       <c r="U20" t="n">
-        <v>1850</v>
+        <v>1364.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1778.083333333333</v>
+        <v>1251.276076253255</v>
       </c>
       <c r="W20" t="n">
-        <v>-39.69044453345396</v>
+        <v>44.93885460905562</v>
       </c>
       <c r="X20" t="n">
-        <v>9.736984121348616</v>
+        <v>57.32524539374285</v>
       </c>
       <c r="Y20" t="n">
-        <v>-49.42742865480257</v>
+        <v>-12.38639078468723</v>
       </c>
       <c r="Z20" t="n">
-        <v>-43.51850691221316</v>
+        <v>0.2166883774044663</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.02095808383233533</v>
+        <v>0.1604938271604939</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.1089918256130791</v>
+        <v>0.430784538209011</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.05610906434111995</v>
+        <v>0.1253428466517092</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.174065390901196</v>
+        <v>0.3657109729208941</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.117956326560076</v>
+        <v>-0.2403681262691848</v>
       </c>
       <c r="AG20" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="AI20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="b">
         <v>0</v>
@@ -3287,11 +3287,15 @@
         <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="n">
-        <v>1934.47</v>
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1551</v>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -3302,12 +3306,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3316,7 +3320,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>35.2</v>
+        <v>39.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3325,24 +3329,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>23519000</v>
+        <v>1000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="K21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>23519000</v>
+        <v>1000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3351,61 +3355,61 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>567</v>
+        <v>105.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>567</v>
+        <v>105.5</v>
       </c>
       <c r="R21" t="n">
-        <v>36099734</v>
+        <v>19016531</v>
       </c>
       <c r="S21" t="n">
-        <v>600.4</v>
+        <v>113.4</v>
       </c>
       <c r="T21" t="n">
-        <v>587.75</v>
+        <v>111.5899997711182</v>
       </c>
       <c r="U21" t="n">
-        <v>586.25</v>
+        <v>110.5349998474121</v>
       </c>
       <c r="V21" t="n">
-        <v>577.275</v>
+        <v>95.91499989827474</v>
       </c>
       <c r="W21" t="n">
-        <v>3.588433587189684</v>
+        <v>1.714176809923558</v>
       </c>
       <c r="X21" t="n">
-        <v>11.3016302944147</v>
+        <v>5.270337076904664</v>
       </c>
       <c r="Y21" t="n">
-        <v>-7.713196707225018</v>
+        <v>-3.556160266981106</v>
       </c>
       <c r="Z21" t="n">
-        <v>-4.110400952110991</v>
+        <v>-2.843717107570888</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.05586592178770955</v>
+        <v>0.249999977401083</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.1537313432835821</v>
+        <v>0.01442307692307687</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.02071494127892493</v>
+        <v>0.2148489968922984</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.218804908571699</v>
+        <v>-0.05065048836504005</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.2395198498506239</v>
+        <v>0.2654994852573385</v>
       </c>
       <c r="AG21" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="AH21" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3423,11 +3427,9 @@
         <v>0</v>
       </c>
       <c r="AN21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>654.3200000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3442,12 +3444,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3456,108 +3458,108 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>34.8</v>
+        <v>36</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3921000</v>
+        <v>7582000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3921000</v>
+        <v>7507000</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.009990675369654988</v>
       </c>
       <c r="P22" t="n">
-        <v>92.30000305175781</v>
+        <v>1635</v>
       </c>
       <c r="Q22" t="n">
-        <v>92.30000305175781</v>
+        <v>1635</v>
       </c>
       <c r="R22" t="n">
-        <v>5955803</v>
+        <v>7401193</v>
       </c>
       <c r="S22" t="n">
-        <v>93.52000122070312</v>
+        <v>1745</v>
       </c>
       <c r="T22" t="n">
-        <v>86.62500038146973</v>
+        <v>1848.25</v>
       </c>
       <c r="U22" t="n">
-        <v>86.06000022888183</v>
+        <v>1850</v>
       </c>
       <c r="V22" t="n">
-        <v>84.74500020345052</v>
+        <v>1778.083333333333</v>
       </c>
       <c r="W22" t="n">
-        <v>2.474931803364896</v>
+        <v>-39.69044453345396</v>
       </c>
       <c r="X22" t="n">
-        <v>1.907505290600312</v>
+        <v>9.73698412134852</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5674265127645846</v>
+        <v>-49.42742865480248</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.8148038556698909</v>
+        <v>-43.51850691221304</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1395062105155285</v>
+        <v>-0.02095808383233533</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.01988953648351166</v>
+        <v>-0.1089918256130791</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.1043552300067438</v>
+        <v>-0.05610906434111995</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.04518402880460526</v>
+        <v>-0.174065390901196</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1495392588113491</v>
+        <v>0.117956326560076</v>
       </c>
       <c r="AG22" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="AH22" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="b">
         <v>0</v>
@@ -3565,15 +3567,9 @@
       <c r="AN22" t="b">
         <v>0</v>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="n">
+        <v>1934.47</v>
       </c>
     </row>
     <row r="23">
@@ -3584,12 +3580,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3598,7 +3594,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>34.40000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3607,24 +3603,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1000</v>
+        <v>23519000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1000</v>
+        <v>23519000</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3633,61 +3629,61 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6400</v>
+        <v>567</v>
       </c>
       <c r="Q23" t="n">
-        <v>6400</v>
+        <v>567</v>
       </c>
       <c r="R23" t="n">
-        <v>4806266</v>
+        <v>35134462</v>
       </c>
       <c r="S23" t="n">
-        <v>6897</v>
+        <v>600.4</v>
       </c>
       <c r="T23" t="n">
-        <v>6497.5</v>
+        <v>587.75</v>
       </c>
       <c r="U23" t="n">
-        <v>6480.25</v>
+        <v>586.25</v>
       </c>
       <c r="V23" t="n">
-        <v>5782.742663574219</v>
+        <v>577.275</v>
       </c>
       <c r="W23" t="n">
-        <v>88.6731949735431</v>
+        <v>3.588433587189684</v>
       </c>
       <c r="X23" t="n">
-        <v>119.5111222848806</v>
+        <v>11.30163029441461</v>
       </c>
       <c r="Y23" t="n">
-        <v>-30.83792731133747</v>
+        <v>-7.713196707224926</v>
       </c>
       <c r="Z23" t="n">
-        <v>22.75795774951959</v>
+        <v>-4.110400952110989</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.05697770437654825</v>
+        <v>0.05586592178770955</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.6206919149641232</v>
+        <v>-0.1537313432835821</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.02182672386776363</v>
+        <v>0.02071494127892493</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.5556183496760063</v>
+        <v>-0.218804908571699</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.5337916258082427</v>
+        <v>0.2395198498506239</v>
       </c>
       <c r="AG23" t="n">
-        <v>56.00000000000001</v>
+        <v>54</v>
       </c>
       <c r="AH23" t="n">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="AI23" t="b">
         <v>0</v>
@@ -3708,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="AO23" t="n">
-        <v>6758.4</v>
+        <v>654.3200000000001</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -3724,12 +3720,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3738,7 +3734,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>33.2</v>
+        <v>35</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3747,15 +3743,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1000</v>
+        <v>3921000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3764,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1000</v>
+        <v>3921000</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3773,82 +3769,84 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3685</v>
+        <v>92.30000305175781</v>
       </c>
       <c r="Q24" t="n">
-        <v>3685</v>
+        <v>92.30000305175781</v>
       </c>
       <c r="R24" t="n">
-        <v>1717320</v>
+        <v>5900291</v>
       </c>
       <c r="S24" t="n">
-        <v>3956</v>
+        <v>93.52000122070312</v>
       </c>
       <c r="T24" t="n">
-        <v>3826.75</v>
+        <v>86.62500038146973</v>
       </c>
       <c r="U24" t="n">
-        <v>3810.25</v>
+        <v>86.06000022888183</v>
       </c>
       <c r="V24" t="n">
-        <v>3750.121183268229</v>
+        <v>84.74500020345052</v>
       </c>
       <c r="W24" t="n">
-        <v>9.753653540336018</v>
+        <v>2.474931803364896</v>
       </c>
       <c r="X24" t="n">
-        <v>60.77968998631973</v>
+        <v>1.907505290600308</v>
       </c>
       <c r="Y24" t="n">
-        <v>-51.02603644598371</v>
+        <v>0.5674265127645881</v>
       </c>
       <c r="Z24" t="n">
-        <v>-25.21574529991113</v>
+        <v>0.8148038556698953</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.09836065573770503</v>
+        <v>0.1395062105155285</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.06412674688517317</v>
+        <v>0.01988953648351166</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.0632096752289204</v>
+        <v>0.1043552300067438</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.0009468184029437499</v>
+        <v>-0.04518402880460526</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.06415649363186415</v>
+        <v>0.1495392588113491</v>
       </c>
       <c r="AG24" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="AH24" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AI24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM24" t="b">
         <v>0</v>
       </c>
       <c r="AN24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>4259.86</v>
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -3864,12 +3862,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3878,24 +3876,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>34.8</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1000</v>
+        <v>654000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3907,73 +3905,73 @@
         <v>1000</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>653000</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="P25" t="n">
-        <v>167.5</v>
+        <v>472</v>
       </c>
       <c r="Q25" t="n">
-        <v>167.5</v>
+        <v>472</v>
       </c>
       <c r="R25" t="n">
-        <v>9654317</v>
+        <v>15256059</v>
       </c>
       <c r="S25" t="n">
-        <v>172.2</v>
+        <v>490.1</v>
       </c>
       <c r="T25" t="n">
-        <v>176.375</v>
+        <v>507.575</v>
       </c>
       <c r="U25" t="n">
-        <v>175.65</v>
+        <v>508.075</v>
       </c>
       <c r="V25" t="n">
-        <v>161.4333333333333</v>
+        <v>453.25</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.2991385622451048</v>
+        <v>-6.440507620384835</v>
       </c>
       <c r="X25" t="n">
-        <v>3.505857435229374</v>
+        <v>3.912199831102828</v>
       </c>
       <c r="Y25" t="n">
-        <v>-3.804995997474479</v>
+        <v>-10.35270745148766</v>
       </c>
       <c r="Z25" t="n">
-        <v>-3.704980493044535</v>
+        <v>-9.644600973429846</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.09477124183006547</v>
+        <v>-0.02074688796680502</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.07717041800643076</v>
+        <v>0.1964512040557669</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.05962026132128084</v>
+        <v>-0.05589786847558964</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.01209685271831384</v>
+        <v>0.13137763876765</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.047523408602967</v>
+        <v>-0.1872755072432396</v>
       </c>
       <c r="AG25" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="AH25" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
       </c>
       <c r="AJ25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="b">
         <v>0</v>
@@ -3988,10 +3986,8 @@
         <v>0</v>
       </c>
       <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP25" t="n">
+        <v>547.45</v>
       </c>
     </row>
     <row r="26">
@@ -4002,12 +3998,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4016,7 +4012,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>32.6</v>
+        <v>34.6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4025,24 +4021,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>12188000</v>
+        <v>1000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="K26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>12188000</v>
+        <v>1000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4051,61 +4047,61 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2420</v>
+        <v>6400</v>
       </c>
       <c r="Q26" t="n">
-        <v>2420</v>
+        <v>6400</v>
       </c>
       <c r="R26" t="n">
-        <v>40787765</v>
+        <v>4442616</v>
       </c>
       <c r="S26" t="n">
-        <v>2476</v>
+        <v>6897</v>
       </c>
       <c r="T26" t="n">
-        <v>2491</v>
+        <v>6497.5</v>
       </c>
       <c r="U26" t="n">
-        <v>2488.9</v>
+        <v>6480.25</v>
       </c>
       <c r="V26" t="n">
-        <v>2416.497591145833</v>
+        <v>5782.742663574219</v>
       </c>
       <c r="W26" t="n">
-        <v>-3.262306824247389</v>
+        <v>88.6731949735431</v>
       </c>
       <c r="X26" t="n">
-        <v>17.31173417264522</v>
+        <v>119.5111222848806</v>
       </c>
       <c r="Y26" t="n">
-        <v>-20.57404099689261</v>
+        <v>-30.83792731133747</v>
       </c>
       <c r="Z26" t="n">
-        <v>-15.91550092530764</v>
+        <v>22.75795774951959</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.01766190075693852</v>
+        <v>0.05697770437654825</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.007105186261707974</v>
+        <v>0.6206919149641232</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.0174890797518461</v>
+        <v>0.02182672386776363</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.05796837902640894</v>
+        <v>0.5556183496760063</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.04047929927456284</v>
+        <v>-0.5337916258082427</v>
       </c>
       <c r="AG26" t="n">
-        <v>38</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH26" t="n">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4126,7 +4122,7 @@
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>2652.32</v>
+        <v>6758.4</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -4142,12 +4138,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4156,7 +4152,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>30.8</v>
+        <v>33.4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4165,7 +4161,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4173,7 +4169,7 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -4191,84 +4187,82 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>101.5</v>
+        <v>3685</v>
       </c>
       <c r="Q27" t="n">
-        <v>101.5</v>
+        <v>3685</v>
       </c>
       <c r="R27" t="n">
-        <v>1884892</v>
+        <v>1554727</v>
       </c>
       <c r="S27" t="n">
-        <v>102.2</v>
+        <v>3956</v>
       </c>
       <c r="T27" t="n">
-        <v>99.99500045776367</v>
+        <v>3826.75</v>
       </c>
       <c r="U27" t="n">
-        <v>99.76500053405762</v>
+        <v>3810.25</v>
       </c>
       <c r="V27" t="n">
-        <v>93.78500022888184</v>
+        <v>3750.121183268229</v>
       </c>
       <c r="W27" t="n">
-        <v>0.936456649952774</v>
+        <v>9.753653540335563</v>
       </c>
       <c r="X27" t="n">
-        <v>0.6580228346008048</v>
+        <v>60.77968998631829</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.2784338153519692</v>
+        <v>-51.02603644598273</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.3747123579904621</v>
+        <v>-25.21574529991035</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.0474716037325611</v>
+        <v>0.09836065573770503</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.2515413305758387</v>
+        <v>0.06412674688517317</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.01232062322377647</v>
+        <v>0.0632096752289204</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.1864677652877218</v>
+        <v>-0.0009468184029437499</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.1741471420639453</v>
+        <v>0.06415649363186415</v>
       </c>
       <c r="AG27" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AH27" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="AI27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
       </c>
       <c r="AK27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="b">
         <v>0</v>
       </c>
       <c r="AN27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>4259.86</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -4284,12 +4278,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4298,7 +4292,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>30.8</v>
+        <v>33.2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4307,15 +4301,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4143450</v>
+        <v>1000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4324,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4143450</v>
+        <v>1000</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4333,61 +4327,61 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>275</v>
+        <v>167.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>275</v>
+        <v>167.5</v>
       </c>
       <c r="R28" t="n">
-        <v>17453696</v>
+        <v>9553134</v>
       </c>
       <c r="S28" t="n">
-        <v>289.7</v>
+        <v>172.2</v>
       </c>
       <c r="T28" t="n">
-        <v>293.825</v>
+        <v>176.375</v>
       </c>
       <c r="U28" t="n">
-        <v>292.925</v>
+        <v>175.65</v>
       </c>
       <c r="V28" t="n">
-        <v>265.2283131917318</v>
+        <v>161.4333333333333</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.5994197869163145</v>
+        <v>-0.2991385622451048</v>
       </c>
       <c r="X28" t="n">
-        <v>4.535897191209456</v>
+        <v>3.505857435229376</v>
       </c>
       <c r="Y28" t="n">
-        <v>-5.13531697812577</v>
+        <v>-3.804995997474481</v>
       </c>
       <c r="Z28" t="n">
-        <v>-4.221953948568109</v>
+        <v>-3.704980493044538</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.07003891050583655</v>
+        <v>0.09477124183006547</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.03889851301655267</v>
+        <v>0.07717041800643076</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.03488792999705193</v>
+        <v>0.05962026132128084</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.02617505227156425</v>
+        <v>0.01209685271831384</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.06106298226861617</v>
+        <v>0.047523408602967</v>
       </c>
       <c r="AG28" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AH28" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4422,12 +4416,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4436,7 +4430,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>29.6</v>
+        <v>31</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4445,15 +4439,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>957000</v>
+        <v>1000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4462,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>957000</v>
+        <v>1000</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4471,82 +4465,84 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>520</v>
+        <v>101.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>520</v>
+        <v>101.5</v>
       </c>
       <c r="R29" t="n">
-        <v>9753012</v>
+        <v>1874677</v>
       </c>
       <c r="S29" t="n">
-        <v>553.4</v>
+        <v>102.2</v>
       </c>
       <c r="T29" t="n">
-        <v>572.25</v>
+        <v>99.99500045776367</v>
       </c>
       <c r="U29" t="n">
-        <v>571.7</v>
+        <v>99.76500053405762</v>
       </c>
       <c r="V29" t="n">
-        <v>539.4833333333333</v>
+        <v>93.78500022888184</v>
       </c>
       <c r="W29" t="n">
-        <v>-9.044624543949112</v>
+        <v>0.936456649952774</v>
       </c>
       <c r="X29" t="n">
-        <v>-2.607043269353864</v>
+        <v>0.6580228346008017</v>
       </c>
       <c r="Y29" t="n">
-        <v>-6.437581274595249</v>
+        <v>0.2784338153519723</v>
       </c>
       <c r="Z29" t="n">
-        <v>-3.527263865473991</v>
+        <v>0.374712357990466</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.0216110019646365</v>
+        <v>0.0474716037325611</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.4565826330532212</v>
+        <v>0.2515413305758387</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.01353997854414812</v>
+        <v>0.01232062322377647</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.3915090677651043</v>
+        <v>0.1864677652877218</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.4050490463092524</v>
+        <v>-0.1741471420639453</v>
       </c>
       <c r="AG29" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AH29" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AI29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
       </c>
       <c r="AK29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM29" t="b">
         <v>0</v>
       </c>
       <c r="AN29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>592.8</v>
+        <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -4562,12 +4558,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4576,7 +4572,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>29.8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4585,15 +4581,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6264000</v>
+        <v>957000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4602,7 +4598,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>6264000</v>
+        <v>957000</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4611,84 +4607,82 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1980</v>
+        <v>520</v>
       </c>
       <c r="Q30" t="n">
-        <v>1980</v>
+        <v>520</v>
       </c>
       <c r="R30" t="n">
-        <v>3530427</v>
+        <v>9436955</v>
       </c>
       <c r="S30" t="n">
-        <v>2030</v>
+        <v>553.4</v>
       </c>
       <c r="T30" t="n">
-        <v>1942.25</v>
+        <v>572.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1935.25</v>
+        <v>571.7</v>
       </c>
       <c r="V30" t="n">
-        <v>2065.462481689453</v>
+        <v>539.4833333333333</v>
       </c>
       <c r="W30" t="n">
-        <v>16.37825705961723</v>
+        <v>-9.044624543949112</v>
       </c>
       <c r="X30" t="n">
-        <v>14.91809795992351</v>
+        <v>-2.607043269353877</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.460159099693712</v>
+        <v>-6.437581274595235</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.986258280959616</v>
+        <v>-3.527263865473973</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.07608695652173902</v>
+        <v>0.0216110019646365</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.1010482715689757</v>
+        <v>0.4565826330532212</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0409359760129544</v>
+        <v>-0.01353997854414812</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.1661218368570926</v>
+        <v>0.3915090677651043</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.207057812870047</v>
+        <v>-0.4050490463092524</v>
       </c>
       <c r="AG30" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="AH30" t="n">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="b">
         <v>1</v>
       </c>
       <c r="AK30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="b">
         <v>0</v>
       </c>
       <c r="AN30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>592.8</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -4704,12 +4698,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4718,7 +4712,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4727,15 +4721,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1000</v>
+        <v>6264000</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4744,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1000</v>
+        <v>6264000</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4753,61 +4747,61 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>81.5</v>
+        <v>1980</v>
       </c>
       <c r="Q31" t="n">
-        <v>81.5</v>
+        <v>1980</v>
       </c>
       <c r="R31" t="n">
-        <v>1313913</v>
+        <v>3397911</v>
       </c>
       <c r="S31" t="n">
-        <v>81.3</v>
+        <v>2030</v>
       </c>
       <c r="T31" t="n">
-        <v>78.61499938964843</v>
+        <v>1942.25</v>
       </c>
       <c r="U31" t="n">
-        <v>78.3699993133545</v>
+        <v>1935.25</v>
       </c>
       <c r="V31" t="n">
-        <v>77.82943280537923</v>
+        <v>2065.462481689453</v>
       </c>
       <c r="W31" t="n">
-        <v>1.080440588135886</v>
+        <v>16.37825705961723</v>
       </c>
       <c r="X31" t="n">
-        <v>0.5948479954566041</v>
+        <v>14.9180979599235</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.485592592679282</v>
+        <v>1.460159099693723</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.5490633083142774</v>
+        <v>7.986258280959628</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.06396868960166291</v>
+        <v>0.07608695652173902</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.01259318436978529</v>
+        <v>-0.1010482715689757</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.02881770909287829</v>
+        <v>0.0409359760129544</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.05248038091833163</v>
+        <v>-0.1661218368570926</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.08129809001120991</v>
+        <v>0.207057812870047</v>
       </c>
       <c r="AG31" t="n">
-        <v>57.99999999999999</v>
+        <v>64</v>
       </c>
       <c r="AH31" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="AI31" t="b">
         <v>1</v>
@@ -4846,12 +4840,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4860,7 +4854,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4869,15 +4863,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4886,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2185000</v>
+        <v>1000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4895,82 +4889,84 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>229</v>
+        <v>81.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>229</v>
+        <v>81.5</v>
       </c>
       <c r="R32" t="n">
-        <v>2285882</v>
+        <v>1304419</v>
       </c>
       <c r="S32" t="n">
-        <v>237.5</v>
+        <v>81.3</v>
       </c>
       <c r="T32" t="n">
-        <v>233.4</v>
+        <v>78.61499938964843</v>
       </c>
       <c r="U32" t="n">
-        <v>233</v>
+        <v>78.3699993133545</v>
       </c>
       <c r="V32" t="n">
-        <v>211.05</v>
+        <v>77.82943280537923</v>
       </c>
       <c r="W32" t="n">
-        <v>1.879829238086529</v>
+        <v>1.080440588135872</v>
       </c>
       <c r="X32" t="n">
-        <v>3.948638719568172</v>
+        <v>0.5948479954565822</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.068809481481643</v>
+        <v>0.4855925926792897</v>
       </c>
       <c r="Z32" t="n">
-        <v>-1.266974247787861</v>
+        <v>0.549063308314287</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.03619909502262453</v>
+        <v>0.06396868960166291</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.1421446384039899</v>
+        <v>0.01259318436978529</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.001048114513839904</v>
+        <v>0.02881770909287829</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.07707107311587302</v>
+        <v>-0.05248038091833163</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.07602295860203312</v>
+        <v>0.08129809001120991</v>
       </c>
       <c r="AG32" t="n">
-        <v>48</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AH32" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="AI32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ32" t="b">
         <v>1</v>
       </c>
       <c r="AK32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="b">
         <v>0</v>
       </c>
       <c r="AN32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>252.36</v>
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -4986,12 +4982,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5000,24 +4996,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5143000</v>
+        <v>2185000</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -5026,76 +5022,76 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5086000</v>
+        <v>2185000</v>
       </c>
       <c r="N33" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.01120723554856469</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4250</v>
+        <v>229</v>
       </c>
       <c r="Q33" t="n">
-        <v>4250</v>
+        <v>229</v>
       </c>
       <c r="R33" t="n">
-        <v>8594719</v>
+        <v>2240743</v>
       </c>
       <c r="S33" t="n">
-        <v>4408</v>
+        <v>237.5</v>
       </c>
       <c r="T33" t="n">
-        <v>4790.5</v>
+        <v>233.4</v>
       </c>
       <c r="U33" t="n">
-        <v>4799.5</v>
+        <v>233</v>
       </c>
       <c r="V33" t="n">
-        <v>4274.5</v>
+        <v>211.05</v>
       </c>
       <c r="W33" t="n">
-        <v>-122.8760504218917</v>
+        <v>1.879829238086529</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.09212629721524124</v>
+        <v>3.948638719568165</v>
       </c>
       <c r="Y33" t="n">
-        <v>-122.7839241246765</v>
+        <v>-2.068809481481636</v>
       </c>
       <c r="Z33" t="n">
-        <v>-127.5067884662056</v>
+        <v>-1.266974247787852</v>
       </c>
       <c r="AA33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.04063205417607219</v>
+        <v>0.03619909502262453</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.1580381471389645</v>
+        <v>0.1421446384039899</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.07578303468485681</v>
+        <v>0.001048114513839904</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.09296458185084755</v>
+        <v>0.07707107311587302</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.1687476165357044</v>
+        <v>-0.07602295860203312</v>
       </c>
       <c r="AG33" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="AH33" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="b">
         <v>0</v>
@@ -5104,14 +5100,18 @@
         <v>0</v>
       </c>
       <c r="AM33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="n">
-        <v>5098.95</v>
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>252.36</v>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5177,7 +5177,7 @@
         <v>158.5</v>
       </c>
       <c r="R34" t="n">
-        <v>13277885</v>
+        <v>13169977</v>
       </c>
       <c r="S34" t="n">
         <v>162.6</v>
@@ -5192,10 +5192,10 @@
         <v>151.2083333333333</v>
       </c>
       <c r="W34" t="n">
-        <v>-1.609375708961352</v>
+        <v>-1.609375708961409</v>
       </c>
       <c r="X34" t="n">
-        <v>1.875328055753662</v>
+        <v>1.875328055753605</v>
       </c>
       <c r="Y34" t="n">
         <v>-3.484703764715014</v>
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5315,7 +5315,7 @@
         <v>133</v>
       </c>
       <c r="R35" t="n">
-        <v>92001831</v>
+        <v>90187620</v>
       </c>
       <c r="S35" t="n">
         <v>139.1</v>
@@ -5333,13 +5333,13 @@
         <v>-3.215749370824284</v>
       </c>
       <c r="X35" t="n">
-        <v>0.3038707882336754</v>
+        <v>0.3038707882336746</v>
       </c>
       <c r="Y35" t="n">
         <v>-3.519620159057959</v>
       </c>
       <c r="Z35" t="n">
-        <v>-3.441758272044087</v>
+        <v>-3.441758272044086</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5410,24 +5410,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>25.4</v>
+        <v>23.6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>201900</v>
+        <v>2887848</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5436,76 +5436,76 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>186900</v>
+        <v>2887848</v>
       </c>
       <c r="N36" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0.08025682182985554</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>16480</v>
+        <v>2015</v>
       </c>
       <c r="Q36" t="n">
-        <v>16480</v>
+        <v>2015</v>
       </c>
       <c r="R36" t="n">
-        <v>310762</v>
+        <v>2095587</v>
       </c>
       <c r="S36" t="n">
-        <v>16994</v>
+        <v>2176</v>
       </c>
       <c r="T36" t="n">
-        <v>18569.5</v>
+        <v>2297</v>
       </c>
       <c r="U36" t="n">
-        <v>18621.5</v>
+        <v>2295.25</v>
       </c>
       <c r="V36" t="n">
-        <v>17089.25</v>
+        <v>2190.75</v>
       </c>
       <c r="W36" t="n">
-        <v>-560.0191406263875</v>
+        <v>-45.04314566761286</v>
       </c>
       <c r="X36" t="n">
-        <v>-175.275731059236</v>
+        <v>22.2816306089634</v>
       </c>
       <c r="Y36" t="n">
-        <v>-384.7434095671516</v>
+        <v>-67.32477627657626</v>
       </c>
       <c r="Z36" t="n">
-        <v>-418.1097860404951</v>
+        <v>-59.64653292198476</v>
       </c>
       <c r="AA36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.05936073059360736</v>
+        <v>0.01767676767676774</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.1687943262411347</v>
+        <v>0.007500000000000062</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.09451171110239198</v>
+        <v>-0.01747421283201689</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.1037207609530177</v>
+        <v>-0.05757356528811686</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.1982324720554097</v>
+        <v>0.04009935245609997</v>
       </c>
       <c r="AG36" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AH36" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
       </c>
       <c r="AJ36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="b">
         <v>0</v>
@@ -5514,14 +5514,16 @@
         <v>0</v>
       </c>
       <c r="AM36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="b">
         <v>0</v>
       </c>
       <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="n">
-        <v>20449.47</v>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -5532,12 +5534,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5546,7 +5548,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5555,15 +5557,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -5572,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1000</v>
+        <v>4328000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5581,67 +5583,67 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>472</v>
+        <v>5165</v>
       </c>
       <c r="Q37" t="n">
-        <v>472</v>
+        <v>5165</v>
       </c>
       <c r="R37" t="n">
-        <v>15781676</v>
+        <v>2553270</v>
       </c>
       <c r="S37" t="n">
-        <v>490.1</v>
+        <v>5500</v>
       </c>
       <c r="T37" t="n">
-        <v>507.575</v>
+        <v>5282.75</v>
       </c>
       <c r="U37" t="n">
-        <v>508.075</v>
+        <v>5280.25</v>
       </c>
       <c r="V37" t="n">
-        <v>453.25</v>
+        <v>5322.909090169271</v>
       </c>
       <c r="W37" t="n">
-        <v>-6.440507620384722</v>
+        <v>25.46163632789285</v>
       </c>
       <c r="X37" t="n">
-        <v>3.912199831102986</v>
+        <v>86.06939147893658</v>
       </c>
       <c r="Y37" t="n">
-        <v>-10.35270745148771</v>
+        <v>-60.60775515104373</v>
       </c>
       <c r="Z37" t="n">
-        <v>-9.644600973429901</v>
+        <v>-26.86192883382469</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.02074688796680502</v>
+        <v>0.009775171065493637</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.1964512040557669</v>
+        <v>0.07424110202656142</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.05589786847558964</v>
+        <v>-0.02537580944329099</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.13137763876765</v>
+        <v>0.009167536738444504</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.1872755072432396</v>
+        <v>-0.03454334618173549</v>
       </c>
       <c r="AG37" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AH37" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
       </c>
       <c r="AJ37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="b">
         <v>0</v>
@@ -5653,11 +5655,15 @@
         <v>0</v>
       </c>
       <c r="AN37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="n">
-        <v>547.45</v>
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>5857.11</v>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -5668,12 +5674,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5691,88 +5697,88 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2887848</v>
+        <v>1000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
+        <v>44</v>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>540</v>
+      </c>
+      <c r="R38" t="n">
+        <v>503564</v>
+      </c>
+      <c r="S38" t="n">
+        <v>547.8</v>
+      </c>
+      <c r="T38" t="n">
+        <v>561.9</v>
+      </c>
+      <c r="U38" t="n">
+        <v>561.05</v>
+      </c>
+      <c r="V38" t="n">
+        <v>566.9836334228515</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-5.293175034313435</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-1.620689590515565</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-3.67248544379787</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-3.375044081717603</v>
+      </c>
+      <c r="AA38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.03250478011472269</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>-0.05940217750113941</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>-0.002646200394061937</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>-0.1244757427892563</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.1218295423951944</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH38" t="n">
         <v>18</v>
       </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="b">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2887848</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2015</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2015</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2221187</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2176</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2297</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2295.25</v>
-      </c>
-      <c r="V38" t="n">
-        <v>2190.75</v>
-      </c>
-      <c r="W38" t="n">
-        <v>-45.04314566761286</v>
-      </c>
-      <c r="X38" t="n">
-        <v>22.28163060896342</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>-67.32477627657627</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>-59.64653292198479</v>
-      </c>
-      <c r="AA38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.01767676767676774</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.007500000000000062</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>-0.01747421283201689</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>-0.05757356528811686</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.04009935245609997</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>32</v>
-      </c>
       <c r="AI38" t="b">
         <v>0</v>
       </c>
@@ -5789,9 +5795,11 @@
         <v>0</v>
       </c>
       <c r="AN38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>582.12</v>
+      </c>
       <c r="AP38" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -5806,12 +5814,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5820,7 +5828,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>23.2</v>
+        <v>20.4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5829,15 +5837,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -5846,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4328000</v>
+        <v>1000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5855,67 +5863,67 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>5165</v>
+        <v>244</v>
       </c>
       <c r="Q39" t="n">
-        <v>5165</v>
+        <v>244</v>
       </c>
       <c r="R39" t="n">
-        <v>2761868</v>
+        <v>49281775</v>
       </c>
       <c r="S39" t="n">
-        <v>5500</v>
+        <v>242.2</v>
       </c>
       <c r="T39" t="n">
-        <v>5282.75</v>
+        <v>249.375</v>
       </c>
       <c r="U39" t="n">
-        <v>5280.25</v>
+        <v>249.5</v>
       </c>
       <c r="V39" t="n">
-        <v>5322.909090169271</v>
+        <v>250.9166666666667</v>
       </c>
       <c r="W39" t="n">
-        <v>25.46163632789376</v>
+        <v>-2.52142207475751</v>
       </c>
       <c r="X39" t="n">
-        <v>86.06939147893755</v>
+        <v>-1.296563832843463</v>
       </c>
       <c r="Y39" t="n">
-        <v>-60.60775515104379</v>
+        <v>-1.224858241914047</v>
       </c>
       <c r="Z39" t="n">
-        <v>-26.86192883382478</v>
+        <v>-1.688914190086806</v>
       </c>
       <c r="AA39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.009775171065493637</v>
+        <v>-0.01014198782961462</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.07424110202656142</v>
+        <v>-0.008130081300813052</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.02537580944329099</v>
+        <v>-0.04529296833839924</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.009167536738444504</v>
+        <v>-0.07320364658892997</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.03454334618173549</v>
+        <v>0.02791067825053073</v>
       </c>
       <c r="AG39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH39" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
       </c>
       <c r="AJ39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="b">
         <v>0</v>
@@ -5924,18 +5932,16 @@
         <v>0</v>
       </c>
       <c r="AM39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN39" t="b">
         <v>1</v>
       </c>
       <c r="AO39" t="n">
-        <v>5857.11</v>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>258.15</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>253.66</v>
       </c>
     </row>
     <row r="40">
@@ -5946,12 +5952,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5960,7 +5966,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>23.2</v>
+        <v>20.2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5969,7 +5975,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -5977,7 +5983,7 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5995,67 +6001,67 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>540</v>
+        <v>447.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>540</v>
+        <v>447.5</v>
       </c>
       <c r="R40" t="n">
-        <v>525680</v>
+        <v>45967146</v>
       </c>
       <c r="S40" t="n">
-        <v>547.8</v>
+        <v>476.5</v>
       </c>
       <c r="T40" t="n">
-        <v>561.9</v>
+        <v>504.5</v>
       </c>
       <c r="U40" t="n">
-        <v>561.05</v>
+        <v>505.4</v>
       </c>
       <c r="V40" t="n">
-        <v>566.9836334228515</v>
+        <v>486.1666666666667</v>
       </c>
       <c r="W40" t="n">
-        <v>-5.293175034313435</v>
+        <v>-13.58907882775202</v>
       </c>
       <c r="X40" t="n">
-        <v>-1.620689590515267</v>
+        <v>-2.506816021675073</v>
       </c>
       <c r="Y40" t="n">
-        <v>-3.672485443798168</v>
+        <v>-11.08226280607695</v>
       </c>
       <c r="Z40" t="n">
-        <v>-3.375044081717863</v>
+        <v>-9.97394763226195</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.03250478011472269</v>
+        <v>-0.03866809881847477</v>
       </c>
       <c r="AC40" t="n">
-        <v>-0.05940217750113941</v>
+        <v>0.1049382716049383</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.002646200394061937</v>
+        <v>-0.0738190793272594</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.1244757427892563</v>
+        <v>0.03986470631682137</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.1218295423951944</v>
+        <v>-0.1136837856440808</v>
       </c>
       <c r="AG40" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AH40" t="n">
-        <v>18</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
       </c>
       <c r="AJ40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="b">
         <v>0</v>
@@ -6067,15 +6073,11 @@
         <v>0</v>
       </c>
       <c r="AN40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>582.12</v>
-      </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="n">
+        <v>552.5</v>
       </c>
     </row>
     <row r="41">
@@ -6086,12 +6088,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6100,7 +6102,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>20.2</v>
+        <v>19.6</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6109,15 +6111,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1000</v>
+        <v>5143000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6126,7 +6128,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1000</v>
+        <v>5143000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6135,61 +6137,61 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>244</v>
+        <v>4250</v>
       </c>
       <c r="Q41" t="n">
-        <v>244</v>
+        <v>4250</v>
       </c>
       <c r="R41" t="n">
-        <v>50072297</v>
+        <v>7757617</v>
       </c>
       <c r="S41" t="n">
-        <v>242.2</v>
+        <v>4408</v>
       </c>
       <c r="T41" t="n">
-        <v>249.375</v>
+        <v>4790.5</v>
       </c>
       <c r="U41" t="n">
-        <v>249.5</v>
+        <v>4799.5</v>
       </c>
       <c r="V41" t="n">
-        <v>250.9166666666667</v>
+        <v>4274.5</v>
       </c>
       <c r="W41" t="n">
-        <v>-2.52142207475751</v>
+        <v>-122.8760504218917</v>
       </c>
       <c r="X41" t="n">
-        <v>-1.296563832843444</v>
+        <v>-0.09212629721524124</v>
       </c>
       <c r="Y41" t="n">
-        <v>-1.224858241914066</v>
+        <v>-122.7839241246765</v>
       </c>
       <c r="Z41" t="n">
-        <v>-1.688914190086831</v>
+        <v>-127.5067884662056</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.01014198782961462</v>
+        <v>-0.04063205417607219</v>
       </c>
       <c r="AC41" t="n">
-        <v>-0.008130081300813052</v>
+        <v>0.1580381471389645</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.04529296833839924</v>
+        <v>-0.07578303468485681</v>
       </c>
       <c r="AE41" t="n">
-        <v>-0.07320364658892997</v>
+        <v>0.09296458185084755</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.02791067825053073</v>
+        <v>-0.1687476165357044</v>
       </c>
       <c r="AG41" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AH41" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6207,13 +6209,11 @@
         <v>1</v>
       </c>
       <c r="AN41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>258.15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="n">
-        <v>253.66</v>
+        <v>5098.95</v>
       </c>
     </row>
     <row r="42">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6247,15 +6247,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6264,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -6273,61 +6273,61 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>447.5</v>
+        <v>3120</v>
       </c>
       <c r="Q42" t="n">
-        <v>447.5</v>
+        <v>3120</v>
       </c>
       <c r="R42" t="n">
-        <v>46975365</v>
+        <v>1049185</v>
       </c>
       <c r="S42" t="n">
-        <v>476.5</v>
+        <v>3189</v>
       </c>
       <c r="T42" t="n">
-        <v>504.5</v>
+        <v>3232</v>
       </c>
       <c r="U42" t="n">
-        <v>505.4</v>
+        <v>3238.75</v>
       </c>
       <c r="V42" t="n">
-        <v>486.1666666666667</v>
+        <v>3011</v>
       </c>
       <c r="W42" t="n">
-        <v>-13.58907882775202</v>
+        <v>-36.18505579455723</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.506816021675073</v>
+        <v>-18.69783317724361</v>
       </c>
       <c r="Y42" t="n">
-        <v>-11.08226280607695</v>
+        <v>-17.48722261731362</v>
       </c>
       <c r="Z42" t="n">
-        <v>-9.97394763226195</v>
+        <v>-21.52010150547788</v>
       </c>
       <c r="AA42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.03866809881847477</v>
+        <v>-0.04147465437788023</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.1049382716049383</v>
+        <v>0.1795841209829867</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.0738190793272594</v>
+        <v>-0.07662563488666485</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.03986470631682137</v>
+        <v>0.1145105556948698</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.1136837856440808</v>
+        <v>-0.1911361905815346</v>
       </c>
       <c r="AG42" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AH42" t="n">
-        <v>57.99999999999999</v>
+        <v>68</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6342,14 +6342,16 @@
         <v>0</v>
       </c>
       <c r="AM42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>3319.68</v>
+      </c>
       <c r="AP42" t="n">
-        <v>552.5</v>
+        <v>3347.89</v>
       </c>
     </row>
     <row r="43">
@@ -6360,12 +6362,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6374,7 +6376,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>19.2</v>
+        <v>18.4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6383,15 +6385,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>470000</v>
+        <v>1000</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6400,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>470000</v>
+        <v>1000</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6409,61 +6411,61 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3120</v>
+        <v>322</v>
       </c>
       <c r="Q43" t="n">
-        <v>3120</v>
+        <v>322</v>
       </c>
       <c r="R43" t="n">
-        <v>1103993</v>
+        <v>9511272</v>
       </c>
       <c r="S43" t="n">
-        <v>3189</v>
+        <v>321.3</v>
       </c>
       <c r="T43" t="n">
-        <v>3232</v>
+        <v>333.075</v>
       </c>
       <c r="U43" t="n">
-        <v>3238.75</v>
+        <v>333.625</v>
       </c>
       <c r="V43" t="n">
-        <v>3011</v>
+        <v>327.05</v>
       </c>
       <c r="W43" t="n">
-        <v>-36.18505579455723</v>
+        <v>-4.266450278084278</v>
       </c>
       <c r="X43" t="n">
-        <v>-18.69783317724341</v>
+        <v>-2.713063747046953</v>
       </c>
       <c r="Y43" t="n">
-        <v>-17.48722261731382</v>
+        <v>-1.553386531037325</v>
       </c>
       <c r="Z43" t="n">
-        <v>-21.52010150547813</v>
+        <v>-2.101321064717312</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.04147465437788023</v>
+        <v>-0.03303303303303307</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.1795841209829867</v>
+        <v>-0.006172839506172867</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.07662563488666485</v>
+        <v>-0.06818401354181769</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.1145105556948698</v>
+        <v>-0.07124640479428979</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.1911361905815346</v>
+        <v>0.003062391252472096</v>
       </c>
       <c r="AG43" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AH43" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6484,10 +6486,10 @@
         <v>1</v>
       </c>
       <c r="AO43" t="n">
-        <v>3319.68</v>
+        <v>340.03</v>
       </c>
       <c r="AP43" t="n">
-        <v>3347.89</v>
+        <v>352.16</v>
       </c>
     </row>
     <row r="44">
@@ -6498,12 +6500,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6512,7 +6514,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6521,7 +6523,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6529,7 +6531,7 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6547,61 +6549,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>322</v>
+        <v>902</v>
       </c>
       <c r="Q44" t="n">
-        <v>322</v>
+        <v>902</v>
       </c>
       <c r="R44" t="n">
-        <v>9667065</v>
+        <v>14865775</v>
       </c>
       <c r="S44" t="n">
-        <v>321.3</v>
+        <v>995</v>
       </c>
       <c r="T44" t="n">
-        <v>333.075</v>
+        <v>1027.65</v>
       </c>
       <c r="U44" t="n">
-        <v>333.625</v>
+        <v>1028.25</v>
       </c>
       <c r="V44" t="n">
-        <v>327.05</v>
+        <v>978.8333333333334</v>
       </c>
       <c r="W44" t="n">
-        <v>-4.266450278084278</v>
+        <v>-13.50961918957125</v>
       </c>
       <c r="X44" t="n">
-        <v>-2.71306374704698</v>
+        <v>22.17543639612178</v>
       </c>
       <c r="Y44" t="n">
-        <v>-1.553386531037298</v>
+        <v>-35.68505558569304</v>
       </c>
       <c r="Z44" t="n">
-        <v>-2.101321064717278</v>
+        <v>-28.26798946627251</v>
       </c>
       <c r="AA44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.03303303303303307</v>
+        <v>-0.01312910284463897</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.006172839506172867</v>
+        <v>-0.2514522821576763</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.06818401354181769</v>
+        <v>-0.0482800833534236</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.07124640479428979</v>
+        <v>-0.3165258474457933</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.003062391252472096</v>
+        <v>0.2682457640923697</v>
       </c>
       <c r="AG44" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AH44" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6616,16 +6618,14 @@
         <v>0</v>
       </c>
       <c r="AM44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>340.03</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="n">
-        <v>352.16</v>
+        <v>1069.26</v>
       </c>
     </row>
     <row r="45">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6685,61 +6685,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>902</v>
+        <v>2000</v>
       </c>
       <c r="Q45" t="n">
-        <v>902</v>
+        <v>2000</v>
       </c>
       <c r="R45" t="n">
-        <v>16344010</v>
+        <v>3436716</v>
       </c>
       <c r="S45" t="n">
-        <v>995</v>
+        <v>2168</v>
       </c>
       <c r="T45" t="n">
-        <v>1027.65</v>
+        <v>2236.75</v>
       </c>
       <c r="U45" t="n">
-        <v>1028.25</v>
+        <v>2240.75</v>
       </c>
       <c r="V45" t="n">
-        <v>978.8333333333334</v>
+        <v>2135</v>
       </c>
       <c r="W45" t="n">
-        <v>-13.50961918957125</v>
+        <v>-32.22265688838252</v>
       </c>
       <c r="X45" t="n">
-        <v>22.17543639612178</v>
+        <v>12.59476629304624</v>
       </c>
       <c r="Y45" t="n">
-        <v>-35.68505558569304</v>
+        <v>-44.81742318142877</v>
       </c>
       <c r="Z45" t="n">
-        <v>-28.26798946627251</v>
+        <v>-32.33166498783359</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.01312910284463897</v>
+        <v>-0.03846153846153844</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.2514522821576763</v>
+        <v>-0.007444168734491274</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.0482800833534236</v>
+        <v>-0.07361251897032306</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.3165258474457933</v>
+        <v>-0.07251773402260819</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.2682457640923697</v>
+        <v>-0.001094784947714866</v>
       </c>
       <c r="AG45" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AH45" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="n">
-        <v>1069.26</v>
+        <v>2339.21</v>
       </c>
     </row>
     <row r="46">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6795,15 +6795,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1000</v>
+        <v>201900</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1000</v>
+        <v>201900</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6821,61 +6821,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2000</v>
+        <v>16480</v>
       </c>
       <c r="Q46" t="n">
-        <v>2000</v>
+        <v>16480</v>
       </c>
       <c r="R46" t="n">
-        <v>3575004</v>
+        <v>284297</v>
       </c>
       <c r="S46" t="n">
-        <v>2168</v>
+        <v>16994</v>
       </c>
       <c r="T46" t="n">
-        <v>2236.75</v>
+        <v>18569.5</v>
       </c>
       <c r="U46" t="n">
-        <v>2240.75</v>
+        <v>18621.5</v>
       </c>
       <c r="V46" t="n">
-        <v>2135</v>
+        <v>17089.25</v>
       </c>
       <c r="W46" t="n">
-        <v>-32.22265688838252</v>
+        <v>-560.0191406263875</v>
       </c>
       <c r="X46" t="n">
-        <v>12.59476629304625</v>
+        <v>-175.2757310592362</v>
       </c>
       <c r="Y46" t="n">
-        <v>-44.81742318142877</v>
+        <v>-384.7434095671514</v>
       </c>
       <c r="Z46" t="n">
-        <v>-32.3316649878336</v>
+        <v>-418.1097860404948</v>
       </c>
       <c r="AA46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.03846153846153844</v>
+        <v>-0.05936073059360736</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.007444168734491274</v>
+        <v>0.1687943262411347</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.07361251897032306</v>
+        <v>-0.09451171110239198</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.07251773402260819</v>
+        <v>0.1037207609530177</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.001094784947714866</v>
+        <v>-0.1982324720554097</v>
       </c>
       <c r="AG46" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AH46" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6890,14 +6890,14 @@
         <v>0</v>
       </c>
       <c r="AM46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN46" t="b">
         <v>0</v>
       </c>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>2339.21</v>
+        <v>20449.47</v>
       </c>
     </row>
     <row r="47">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6963,7 +6963,7 @@
         <v>1845</v>
       </c>
       <c r="R47" t="n">
-        <v>13372287</v>
+        <v>12287772</v>
       </c>
       <c r="S47" t="n">
         <v>2067</v>
@@ -6981,13 +6981,13 @@
         <v>-62.78250070016929</v>
       </c>
       <c r="X47" t="n">
-        <v>-25.23301919947082</v>
+        <v>-25.233019199471</v>
       </c>
       <c r="Y47" t="n">
-        <v>-37.54948150069847</v>
+        <v>-37.54948150069829</v>
       </c>
       <c r="Z47" t="n">
-        <v>-19.84982888075157</v>
+        <v>-19.84982888075135</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -7058,7 +7058,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7099,7 +7099,7 @@
         <v>5205</v>
       </c>
       <c r="R48" t="n">
-        <v>1540825</v>
+        <v>1463336</v>
       </c>
       <c r="S48" t="n">
         <v>5692</v>
@@ -7114,16 +7114,16 @@
         <v>5588.083333333333</v>
       </c>
       <c r="W48" t="n">
-        <v>6.001759798634339</v>
+        <v>6.001759798633429</v>
       </c>
       <c r="X48" t="n">
-        <v>37.92903167516392</v>
+        <v>37.92903167516284</v>
       </c>
       <c r="Y48" t="n">
-        <v>-31.92727187652958</v>
+        <v>-31.92727187652941</v>
       </c>
       <c r="Z48" t="n">
-        <v>14.85854463919038</v>
+        <v>14.8585446391906</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7237,7 +7237,7 @@
         <v>834</v>
       </c>
       <c r="R49" t="n">
-        <v>639403</v>
+        <v>585807</v>
       </c>
       <c r="S49" t="n">
         <v>843.8</v>
@@ -7255,13 +7255,13 @@
         <v>-16.27706785386522</v>
       </c>
       <c r="X49" t="n">
-        <v>-15.85999939419889</v>
+        <v>-15.85999939419888</v>
       </c>
       <c r="Y49" t="n">
-        <v>-0.4170684596663303</v>
+        <v>-0.4170684596663357</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.06517666901736874</v>
+        <v>0.06517666901736163</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7375,7 +7375,7 @@
         <v>1155</v>
       </c>
       <c r="R50" t="n">
-        <v>533893</v>
+        <v>504166</v>
       </c>
       <c r="S50" t="n">
         <v>1175</v>
@@ -7393,13 +7393,13 @@
         <v>-26.61889905514317</v>
       </c>
       <c r="X50" t="n">
-        <v>-28.8663499024008</v>
+        <v>-28.86634990240082</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.247450847257628</v>
+        <v>2.247450847257646</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.503943354691707</v>
+        <v>3.503943354691728</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>5160</v>
       </c>
       <c r="R51" t="n">
-        <v>790793</v>
+        <v>735494</v>
       </c>
       <c r="S51" t="n">
         <v>5511</v>
@@ -7533,13 +7533,13 @@
         <v>-251.3873140364049</v>
       </c>
       <c r="X51" t="n">
-        <v>-188.2618667969099</v>
+        <v>-188.2618667969104</v>
       </c>
       <c r="Y51" t="n">
-        <v>-63.12544723949495</v>
+        <v>-63.12544723949443</v>
       </c>
       <c r="Z51" t="n">
-        <v>-51.03017474922342</v>
+        <v>-51.03017474922279</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
